--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -1,31 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\bigProjects\Internship_Summer\Route_Price_Prediction\data\master\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEF5C846-D979-4D80-87DE-4AE6C08C1CAF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="10380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="10380"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="36">
   <si>
     <t>Truck Type</t>
   </si>
@@ -78,10 +67,34 @@
     <t>20 Feet</t>
   </si>
   <si>
+    <t>20 Feet Trailor</t>
+  </si>
+  <si>
+    <t>2500</t>
+  </si>
+  <si>
+    <t>5.5</t>
+  </si>
+  <si>
+    <t>4.5</t>
+  </si>
+  <si>
+    <t>350</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
     <t>22 Feet</t>
   </si>
   <si>
     <t>24 Feet</t>
+  </si>
+  <si>
+    <t>24 feet Trailor</t>
+  </si>
+  <si>
+    <t>2,600</t>
   </si>
   <si>
     <t>32 JCB</t>
@@ -114,37 +127,31 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
+      <sz val="11"/>
       <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <color theme="1"/>
+      <scheme val="minor"/>
       <sz val="10"/>
-      <color theme="1"/>
       <name val="Calibri"/>
-      <scheme val="minor"/>
     </font>
     <font>
+      <color theme="1"/>
+      <scheme val="minor"/>
       <sz val="10"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <color theme="1"/>
+      <sz val="10"/>
       <name val="Arial"/>
     </font>
   </fonts>
@@ -177,31 +184,27 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-00002F000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -478,15 +481,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F25"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="20.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.5546875" customWidth="1"/>
+    <col min="4" max="4" width="14.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -506,443 +509,483 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2" s="3">
         <v>900</v>
       </c>
-      <c r="C2" s="5">
+      <c r="C2" s="4">
         <v>12</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="3">
         <v>2</v>
       </c>
-      <c r="E2" s="4">
+      <c r="E2" s="3">
         <v>500</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F2" s="3">
         <v>1.75</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="7" t="s">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="5">
         <v>2500</v>
       </c>
-      <c r="C3" s="8">
+      <c r="C3" s="6">
         <v>4.5</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="5">
         <v>8</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="5">
         <v>300</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="5">
         <v>5.5</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="5">
         <v>830</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="5">
         <v>8.5</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="5">
         <v>2.25</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="5">
         <v>500</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="7" t="s">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="5">
         <v>2500</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="6">
         <v>3.8</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="5">
         <v>8.5</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="5">
         <v>300</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="5">
         <v>5.5</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="2">
         <v>1150</v>
       </c>
-      <c r="C6" s="9">
+      <c r="C6" s="7">
         <v>8</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="2">
         <v>2.25</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="2">
         <v>400</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="2">
         <v>2.5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="5">
         <v>1150</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="6">
         <v>8</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="5">
         <v>2.25</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="5">
         <v>400</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="5">
         <v>2500</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="6">
         <v>3.2</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="5">
         <v>9</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="5">
         <v>300</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="5">
         <v>5.5</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="7" t="s">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="5">
         <v>2500</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="5">
         <v>3</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="5">
         <v>9.5</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="5">
         <v>300</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="5">
         <v>6.5</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="5">
         <v>1150</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10" s="6">
         <v>7</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10" s="5">
         <v>2.5</v>
       </c>
-      <c r="E10" s="2">
+      <c r="E10" s="5">
         <v>400</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="5">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="7" t="s">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="5">
         <v>1150</v>
       </c>
-      <c r="C11" s="8">
+      <c r="C11" s="6">
         <v>6.5</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11" s="5">
         <v>2.75</v>
       </c>
-      <c r="E11" s="2">
+      <c r="E11" s="5">
         <v>400</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="5">
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="4">
+      <c r="B12" s="3">
         <v>1600</v>
       </c>
-      <c r="C12" s="5">
+      <c r="C12" s="4">
         <v>7.3</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12" s="3">
         <v>2.75</v>
       </c>
-      <c r="E12" s="4">
+      <c r="E12" s="3">
         <v>400</v>
       </c>
-      <c r="F12" s="4">
+      <c r="F12" s="3">
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="7" t="s">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="5">
         <v>1650</v>
       </c>
-      <c r="C13" s="8">
+      <c r="C14" s="6">
         <v>5.8</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D14" s="5">
         <v>4.5</v>
       </c>
-      <c r="E13" s="2">
+      <c r="E14" s="5">
         <v>400</v>
       </c>
-      <c r="F13" s="2">
+      <c r="F14" s="5">
         <v>4.5</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B14" s="2">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="5">
         <v>1650</v>
       </c>
-      <c r="C14" s="8">
+      <c r="C15" s="6">
         <v>5.5</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D15" s="5">
         <v>4.5</v>
       </c>
-      <c r="E14" s="2">
+      <c r="E15" s="5">
         <v>400</v>
       </c>
-      <c r="F14" s="2">
+      <c r="F15" s="5">
         <v>4.5</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D16" t="s">
+        <v>22</v>
+      </c>
+      <c r="E16" t="s">
+        <v>21</v>
+      </c>
+      <c r="F16" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="2">
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" s="5">
         <v>2500</v>
       </c>
-      <c r="C15" s="8">
+      <c r="C17" s="6">
         <v>3.5</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D17" s="5">
         <v>8</v>
       </c>
-      <c r="E15" s="2">
+      <c r="E17" s="5">
         <v>350</v>
       </c>
-      <c r="F15" s="2">
+      <c r="F17" s="5">
         <v>5.5</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B16" s="2">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" s="5">
         <v>2500</v>
       </c>
-      <c r="C16" s="8">
+      <c r="C18" s="6">
         <v>3.5</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D18" s="5">
         <v>8</v>
       </c>
-      <c r="E16" s="2">
+      <c r="E18" s="5">
         <v>350</v>
       </c>
-      <c r="F16" s="2">
+      <c r="F18" s="5">
         <v>5.5</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B17" s="2">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" s="5">
         <v>2500</v>
       </c>
-      <c r="C17" s="8">
+      <c r="C19" s="6">
         <v>4</v>
       </c>
-      <c r="D17" s="2">
+      <c r="D19" s="5">
         <v>6</v>
       </c>
-      <c r="E17" s="2">
+      <c r="E19" s="5">
         <v>350</v>
       </c>
-      <c r="F17" s="2">
+      <c r="F19" s="5">
         <v>5.5</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B18" s="2">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B20" s="5">
         <v>3300</v>
       </c>
-      <c r="C18" s="8">
+      <c r="C20" s="6">
         <v>2.6</v>
       </c>
-      <c r="D18" s="2">
+      <c r="D20" s="5">
         <v>8.5</v>
       </c>
-      <c r="E18" s="2">
+      <c r="E20" s="5">
         <v>300</v>
       </c>
-      <c r="F18" s="2">
+      <c r="F20" s="5">
         <v>5.5</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B19" s="2">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21" s="5">
         <v>3300</v>
       </c>
-      <c r="C19" s="8">
+      <c r="C21" s="6">
         <v>2.5</v>
       </c>
-      <c r="D19" s="2">
+      <c r="D21" s="5">
         <v>8.5</v>
       </c>
-      <c r="E19" s="2">
+      <c r="E21" s="5">
         <v>300</v>
       </c>
-      <c r="F19" s="2">
+      <c r="F21" s="5">
         <v>5.5</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B20" s="2">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B22" s="5">
         <v>3300</v>
       </c>
-      <c r="C20" s="2">
+      <c r="C22" s="5">
         <v>2.6</v>
       </c>
-      <c r="D20" s="2">
+      <c r="D22" s="5">
         <v>9</v>
       </c>
-      <c r="E20" s="2">
+      <c r="E22" s="5">
         <v>300</v>
       </c>
-      <c r="F20" s="2">
+      <c r="F22" s="5">
         <v>6.5</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B21" s="2">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B23" s="5">
         <v>500</v>
       </c>
-      <c r="C21" s="8">
+      <c r="C23" s="6">
         <v>17</v>
       </c>
-      <c r="D21" s="2">
+      <c r="D23" s="5">
         <v>1.5</v>
       </c>
-      <c r="E21" s="2">
+      <c r="E23" s="5">
         <v>500</v>
       </c>
-      <c r="F21" s="2">
+      <c r="F23" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B22" s="4">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B24" s="3">
         <v>500</v>
       </c>
-      <c r="C22" s="5">
+      <c r="C24" s="4">
         <v>14</v>
       </c>
-      <c r="D22" s="4">
+      <c r="D24" s="3">
         <v>1.5</v>
       </c>
-      <c r="E22" s="4">
+      <c r="E24" s="3">
         <v>500</v>
       </c>
-      <c r="F22" s="4">
+      <c r="F24" s="3">
         <v>1.75</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B23" s="4">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B25" s="3">
         <v>500</v>
       </c>
-      <c r="C23" s="5">
+      <c r="C25" s="4">
         <v>12</v>
       </c>
-      <c r="D23" s="4">
+      <c r="D25" s="3">
         <v>1.75</v>
       </c>
-      <c r="E23" s="4">
+      <c r="E25" s="3">
         <v>500</v>
       </c>
-      <c r="F23" s="4">
+      <c r="F25" s="3">
         <v>1.75</v>
       </c>
     </row>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20417"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A09532A0-0DD5-4397-98DB-5B809C87CC6B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="10380"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="10380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>Truck Type</t>
   </si>
@@ -70,21 +71,6 @@
     <t>20 Feet Trailor</t>
   </si>
   <si>
-    <t>2500</t>
-  </si>
-  <si>
-    <t>5.5</t>
-  </si>
-  <si>
-    <t>4.5</t>
-  </si>
-  <si>
-    <t>350</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
     <t>22 Feet</t>
   </si>
   <si>
@@ -92,9 +78,6 @@
   </si>
   <si>
     <t>24 feet Trailor</t>
-  </si>
-  <si>
-    <t>2,600</t>
   </si>
   <si>
     <t>32 JCB</t>
@@ -127,31 +110,31 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
-      <sz val="10"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
-      <sz val="10"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
-      <sz val="10"/>
       <name val="Arial"/>
     </font>
   </fonts>
@@ -187,7 +170,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -202,6 +185,8 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -481,9 +466,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F25"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.5546875" customWidth="1"/>
     <col min="4" max="4" width="14.33203125" customWidth="1"/>
@@ -733,25 +718,25 @@
       <c r="A13" t="s">
         <v>17</v>
       </c>
-      <c r="B13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F13" t="s">
-        <v>22</v>
+      <c r="B13" s="8">
+        <v>2500</v>
+      </c>
+      <c r="C13" s="8">
+        <v>5.5</v>
+      </c>
+      <c r="D13" s="8">
+        <v>4.5</v>
+      </c>
+      <c r="E13" s="8">
+        <v>350</v>
+      </c>
+      <c r="F13" s="8">
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B14" s="5">
         <v>1650</v>
@@ -771,7 +756,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B15" s="5">
         <v>1650</v>
@@ -791,27 +776,27 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>25</v>
-      </c>
-      <c r="B16" t="s">
-        <v>26</v>
-      </c>
-      <c r="C16" t="s">
-        <v>22</v>
-      </c>
-      <c r="D16" t="s">
-        <v>22</v>
-      </c>
-      <c r="E16" t="s">
-        <v>21</v>
-      </c>
-      <c r="F16" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="B16" s="9">
+        <v>2600</v>
+      </c>
+      <c r="C16" s="8">
+        <v>5</v>
+      </c>
+      <c r="D16" s="8">
+        <v>5</v>
+      </c>
+      <c r="E16" s="8">
+        <v>350</v>
+      </c>
+      <c r="F16" s="8">
+        <v>5.5</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B17" s="5">
         <v>2500</v>
@@ -831,7 +816,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B18" s="5">
         <v>2500</v>
@@ -851,7 +836,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B19" s="5">
         <v>2500</v>
@@ -871,7 +856,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B20" s="5">
         <v>3300</v>
@@ -891,7 +876,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B21" s="5">
         <v>3300</v>
@@ -911,7 +896,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B22" s="5">
         <v>3300</v>
@@ -931,7 +916,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B23" s="5">
         <v>500</v>
@@ -951,7 +936,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B24" s="3">
         <v>500</v>
@@ -971,7 +956,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B25" s="3">
         <v>500</v>
